--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3195876288659794</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="B2">
-        <v>0.03225806451612903</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.323943661971831</v>
+        <v>0.35</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>0.728</v>
       </c>
       <c r="E2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3469387755102041</v>
+        <v>0.3191489361702128</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="C2">
-        <v>0.35</v>
+        <v>0.3695652173913043</v>
       </c>
       <c r="D2">
-        <v>0.728</v>
+        <v>0.7372881355932204</v>
       </c>
       <c r="E2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
